--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 자원 데이터 테이블_보상 테이블용V1.8.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 자원 데이터 테이블_보상 테이블용V1.8.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\이기석\이벤트 보상 테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\데이터 테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E04DF8-7960-4AEF-BDE2-96CCD61F297A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368D6969-C30A-4DD8-9CCD-BCA37CD918E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="898" firstSheet="1" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="898" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문서 개요" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="511">
   <si>
     <t>《Hero Influence》 자원 데이터 테이블</t>
   </si>
@@ -1321,21 +1321,12 @@
     <t>103101</t>
   </si>
   <si>
-    <t>메인퀘스트3 클리어 / 인질 3명 부상</t>
-  </si>
-  <si>
     <t>103102</t>
   </si>
   <si>
-    <t>메인퀘스트3 클리어 / 인질 1~2명 부상</t>
-  </si>
-  <si>
     <t>103103</t>
   </si>
   <si>
-    <t>메인퀘스트3 클리어 / 인질 모두 구출</t>
-  </si>
-  <si>
     <t>104101</t>
   </si>
   <si>
@@ -1381,12 +1372,6 @@
     <t>메인퀘스트2-1 승리 / 편의점 빌런 완료</t>
   </si>
   <si>
-    <t>102151</t>
-  </si>
-  <si>
-    <t>메인퀘스트2-1 승리 / 편의점 빌런 완료 + 소녀 동행</t>
-  </si>
-  <si>
     <t>102211</t>
   </si>
   <si>
@@ -1523,10 +1508,6 @@
   </si>
   <si>
     <t>밸런스 판정</t>
-  </si>
-  <si>
-    <t>서브퀘스트2 완료 / 메인 클리어 전 숨은 자원 보상</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>경험치/4</t>
@@ -1573,10 +1554,6 @@
   </si>
   <si>
     <t>서브퀘스트2 패배</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인퀘스트3 패배</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1688,6 +1665,46 @@
   </si>
   <si>
     <t>메인퀘스트6 패배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2구역_UMT 아놀드 전투 승리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브퀘스트2 완료 / 메인 클리어 전 자원 보상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인퀘스트 보스1 클리어 / 인질 1~2명 부상</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인퀘스트 보스1 클리어 / 인질 모두 구출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인퀘스트 보스1 패배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IP 총합</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인퀘스트 보스1 클리어 / 인질 3명 부상(상의 필요)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건부 아래 I.P 추가 보상 옵션 제공</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인질 미보호 시, 강한 패널티 부여</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1755,7 +1772,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1830,6 +1847,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1927,7 +1950,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2026,12 +2049,14 @@
     <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2071,7 +2096,24 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
@@ -3169,11 +3211,11 @@
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
     </row>
     <row r="13" spans="1:6" ht="409.5" x14ac:dyDescent="0.3">
       <c r="B13" s="33" t="s">
@@ -3189,11 +3231,11 @@
       <c r="A15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="1:6" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -3215,11 +3257,11 @@
       <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="1:6" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -3236,11 +3278,11 @@
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:6" ht="198" x14ac:dyDescent="0.3">
       <c r="B22" s="33" t="s">
@@ -5339,12 +5381,12 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A2:AB61"/>
+  <dimension ref="A2:AD62"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="32" customWidth="1"/>
     <col min="2" max="2" width="15" style="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.625" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.875" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="32" customWidth="1"/>
     <col min="5" max="5" width="11.625" style="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.75" style="32" bestFit="1" customWidth="1"/>
@@ -5369,59 +5411,60 @@
     <col min="26" max="26" width="18" style="32" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.5" style="32" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.625" style="32" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="9" style="32" customWidth="1"/>
+    <col min="29" max="29" width="9" style="32" customWidth="1"/>
+    <col min="30" max="30" width="34.625" style="32" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="9" style="32"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+    <row r="2" spans="1:30" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="53" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="55" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="47" t="s">
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="49" t="s">
         <v>336</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="48" t="s">
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="50" t="s">
         <v>337</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="50" t="s">
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="49" t="s">
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="46"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="48"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>340</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="25" t="s">
         <v>40</v>
       </c>
@@ -5435,7 +5478,7 @@
         <v>52</v>
       </c>
       <c r="H3" s="25" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="I3" s="27" t="s">
         <v>342</v>
@@ -5498,7 +5541,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>347</v>
       </c>
@@ -5521,7 +5564,7 @@
         <v>353</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>354</v>
@@ -5583,9 +5626,15 @@
       <c r="AB4" s="30" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B5" s="31" t="s">
+      <c r="AC4" s="39" t="s">
+        <v>506</v>
+      </c>
+      <c r="AD4" s="39" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B5" s="62" t="s">
         <v>374</v>
       </c>
       <c r="C5" s="31" t="s">
@@ -5601,36 +5650,40 @@
       </c>
       <c r="H5" s="30"/>
       <c r="I5" s="30">
-        <v>-50</v>
+        <v>-7</v>
       </c>
       <c r="J5" s="30"/>
       <c r="K5" s="30"/>
       <c r="L5" s="30"/>
       <c r="M5" s="30"/>
       <c r="N5" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O5" s="30"/>
       <c r="P5" s="30"/>
       <c r="Q5" s="30"/>
       <c r="R5" s="30"/>
       <c r="S5" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" s="30"/>
       <c r="U5" s="30"/>
       <c r="V5" s="30"/>
       <c r="W5" s="30"/>
       <c r="X5" s="30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5" s="30"/>
       <c r="Z5" s="30"/>
       <c r="AA5" s="30"/>
       <c r="AB5" s="30"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
+      <c r="AC5" s="32">
+        <f>SUM(I5,N5,S5,X5)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B6" s="62" t="s">
         <v>376</v>
       </c>
       <c r="C6" s="31" t="s">
@@ -5646,36 +5699,40 @@
       </c>
       <c r="H6" s="30"/>
       <c r="I6" s="30">
-        <v>-20</v>
+        <v>9</v>
       </c>
       <c r="J6" s="30"/>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
       <c r="M6" s="30"/>
       <c r="N6" s="30">
-        <v>-20</v>
+        <v>9</v>
       </c>
       <c r="O6" s="30"/>
       <c r="P6" s="30"/>
       <c r="Q6" s="30"/>
       <c r="R6" s="30"/>
       <c r="S6" s="30">
-        <v>-20</v>
+        <v>9</v>
       </c>
       <c r="T6" s="30"/>
       <c r="U6" s="30"/>
       <c r="V6" s="30"/>
       <c r="W6" s="30"/>
       <c r="X6" s="30">
-        <v>-50</v>
+        <v>-7</v>
       </c>
       <c r="Y6" s="30"/>
       <c r="Z6" s="30"/>
       <c r="AA6" s="30"/>
       <c r="AB6" s="30"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B7" s="31" t="s">
+      <c r="AC6" s="32">
+        <f t="shared" ref="AC6:AC61" si="0">SUM(I6,N6,S6,X6)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B7" s="62" t="s">
         <v>378</v>
       </c>
       <c r="C7" s="31" t="s">
@@ -5687,36 +5744,40 @@
       <c r="G7" s="30"/>
       <c r="H7" s="30"/>
       <c r="I7" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
       <c r="M7" s="30"/>
       <c r="N7" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O7" s="30"/>
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="30"/>
       <c r="S7" s="30">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="T7" s="30"/>
       <c r="U7" s="30"/>
       <c r="V7" s="30"/>
       <c r="W7" s="30"/>
       <c r="X7" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="30"/>
       <c r="Z7" s="30"/>
       <c r="AA7" s="30"/>
       <c r="AB7" s="30"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B8" s="31" t="s">
+      <c r="AC7" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B8" s="62" t="s">
         <v>380</v>
       </c>
       <c r="C8" s="31" t="s">
@@ -5728,36 +5789,40 @@
       <c r="G8" s="30"/>
       <c r="H8" s="30"/>
       <c r="I8" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="30"/>
       <c r="L8" s="30"/>
       <c r="M8" s="30"/>
       <c r="N8" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O8" s="30"/>
       <c r="P8" s="30"/>
       <c r="Q8" s="30"/>
       <c r="R8" s="30"/>
       <c r="S8" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T8" s="30"/>
       <c r="U8" s="30"/>
       <c r="V8" s="30"/>
       <c r="W8" s="30"/>
       <c r="X8" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y8" s="30"/>
       <c r="Z8" s="30"/>
       <c r="AA8" s="30"/>
       <c r="AB8" s="30"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B9" s="31" t="s">
+      <c r="AC8" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B9" s="62" t="s">
         <v>382</v>
       </c>
       <c r="C9" s="31" t="s">
@@ -5769,36 +5834,40 @@
       <c r="G9" s="30"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
       <c r="M9" s="30"/>
       <c r="N9" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O9" s="30"/>
       <c r="P9" s="30"/>
       <c r="Q9" s="30"/>
       <c r="R9" s="30"/>
       <c r="S9" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T9" s="30"/>
       <c r="U9" s="30"/>
       <c r="V9" s="30"/>
       <c r="W9" s="30"/>
       <c r="X9" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="30"/>
       <c r="Z9" s="30"/>
       <c r="AA9" s="30"/>
       <c r="AB9" s="30"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B10" s="31" t="s">
+      <c r="AC9" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B10" s="62" t="s">
         <v>384</v>
       </c>
       <c r="C10" s="31" t="s">
@@ -5810,36 +5879,40 @@
       <c r="G10" s="30"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O10" s="30"/>
       <c r="P10" s="30"/>
       <c r="Q10" s="30"/>
       <c r="R10" s="30"/>
       <c r="S10" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T10" s="30"/>
       <c r="U10" s="30"/>
       <c r="V10" s="30"/>
       <c r="W10" s="30"/>
       <c r="X10" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y10" s="30"/>
       <c r="Z10" s="30"/>
       <c r="AA10" s="30"/>
       <c r="AB10" s="30"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B11" s="31" t="s">
+      <c r="AC10" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B11" s="62" t="s">
         <v>386</v>
       </c>
       <c r="C11" s="31" t="s">
@@ -5851,36 +5924,40 @@
       <c r="G11" s="30"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
       <c r="N11" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O11" s="30"/>
       <c r="P11" s="30"/>
       <c r="Q11" s="30"/>
       <c r="R11" s="30"/>
       <c r="S11" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T11" s="30"/>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
       <c r="W11" s="30"/>
       <c r="X11" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="30"/>
       <c r="Z11" s="30"/>
       <c r="AA11" s="30"/>
       <c r="AB11" s="30"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B12" s="31" t="s">
+      <c r="AC11" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B12" s="62" t="s">
         <v>388</v>
       </c>
       <c r="C12" s="31" t="s">
@@ -5892,36 +5969,40 @@
       <c r="G12" s="30"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
       <c r="N12" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
       <c r="R12" s="30"/>
       <c r="S12" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T12" s="30"/>
       <c r="U12" s="30"/>
       <c r="V12" s="30"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y12" s="30"/>
       <c r="Z12" s="30"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="30"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B13" s="31" t="s">
+      <c r="AC12" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B13" s="62" t="s">
         <v>390</v>
       </c>
       <c r="C13" s="31" t="s">
@@ -5933,36 +6014,40 @@
       <c r="G13" s="30"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="30"/>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
       <c r="M13" s="30"/>
       <c r="N13" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O13" s="30"/>
       <c r="P13" s="30"/>
       <c r="Q13" s="30"/>
       <c r="R13" s="30"/>
       <c r="S13" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T13" s="30"/>
       <c r="U13" s="30"/>
       <c r="V13" s="30"/>
       <c r="W13" s="30"/>
       <c r="X13" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="30"/>
       <c r="Z13" s="30"/>
       <c r="AA13" s="30"/>
       <c r="AB13" s="30"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B14" s="31" t="s">
+      <c r="AC13" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B14" s="62" t="s">
         <v>392</v>
       </c>
       <c r="C14" s="31" t="s">
@@ -5974,36 +6059,40 @@
       <c r="G14" s="30"/>
       <c r="H14" s="30"/>
       <c r="I14" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
       <c r="M14" s="30"/>
       <c r="N14" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O14" s="30"/>
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="30"/>
       <c r="S14" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" s="30"/>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
       <c r="W14" s="30"/>
       <c r="X14" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="30"/>
       <c r="Z14" s="30"/>
       <c r="AA14" s="30"/>
       <c r="AB14" s="30"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B15" s="31" t="s">
+      <c r="AC14" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B15" s="62" t="s">
         <v>394</v>
       </c>
       <c r="C15" s="31" t="s">
@@ -6015,81 +6104,92 @@
       <c r="G15" s="30"/>
       <c r="H15" s="30"/>
       <c r="I15" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30"/>
       <c r="L15" s="30"/>
       <c r="M15" s="30"/>
       <c r="N15" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O15" s="30"/>
       <c r="P15" s="30"/>
       <c r="Q15" s="30"/>
       <c r="R15" s="30"/>
       <c r="S15" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T15" s="30"/>
       <c r="U15" s="30"/>
       <c r="V15" s="30"/>
       <c r="W15" s="30"/>
       <c r="X15" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="30"/>
       <c r="Z15" s="30"/>
       <c r="AA15" s="30"/>
       <c r="AB15" s="30"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B16" s="31" t="s">
+      <c r="AC15" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="B16" s="63" t="s">
         <v>396</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="43" t="s">
+        <v>507</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41">
+        <v>-10</v>
+      </c>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41">
+        <v>-10</v>
+      </c>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41">
+        <v>-10</v>
+      </c>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41">
+        <v>-10</v>
+      </c>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="41"/>
+      <c r="AA16" s="41"/>
+      <c r="AB16" s="41"/>
+      <c r="AC16" s="40">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="AD16" s="40" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B17" s="62" t="s">
         <v>397</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30">
-        <v>-50</v>
-      </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30">
-        <v>-50</v>
-      </c>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30">
-        <v>-50</v>
-      </c>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="30"/>
-      <c r="X16" s="30">
-        <v>-50</v>
-      </c>
-      <c r="Y16" s="30"/>
-      <c r="Z16" s="30"/>
-      <c r="AA16" s="30"/>
-      <c r="AB16" s="30"/>
-    </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B17" s="31" t="s">
-        <v>398</v>
-      </c>
       <c r="C17" s="31" t="s">
-        <v>399</v>
+        <v>503</v>
       </c>
       <c r="D17" s="30"/>
       <c r="E17" s="30"/>
@@ -6097,40 +6197,44 @@
       <c r="G17" s="30"/>
       <c r="H17" s="30"/>
       <c r="I17" s="30">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
       <c r="L17" s="30"/>
       <c r="M17" s="30"/>
       <c r="N17" s="30">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="O17" s="30"/>
       <c r="P17" s="30"/>
       <c r="Q17" s="30"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="T17" s="30"/>
       <c r="U17" s="30"/>
       <c r="V17" s="30"/>
       <c r="W17" s="30"/>
       <c r="X17" s="30">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="30"/>
       <c r="Z17" s="30"/>
       <c r="AA17" s="30"/>
       <c r="AB17" s="30"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B18" s="31" t="s">
-        <v>400</v>
+      <c r="AC17" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B18" s="62" t="s">
+        <v>398</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>401</v>
+        <v>504</v>
       </c>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
@@ -6138,40 +6242,44 @@
       <c r="G18" s="30"/>
       <c r="H18" s="30"/>
       <c r="I18" s="30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
       <c r="L18" s="30"/>
       <c r="M18" s="30"/>
       <c r="N18" s="30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="O18" s="30"/>
       <c r="P18" s="30"/>
       <c r="Q18" s="30"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" s="30"/>
       <c r="U18" s="30"/>
       <c r="V18" s="30"/>
       <c r="W18" s="30"/>
       <c r="X18" s="30">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="Y18" s="30"/>
       <c r="Z18" s="30"/>
       <c r="AA18" s="30"/>
       <c r="AB18" s="30"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B19" s="31" t="s">
-        <v>479</v>
+      <c r="AC18" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B19" s="62" t="s">
+        <v>472</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
@@ -6179,75 +6287,89 @@
       <c r="G19" s="30"/>
       <c r="H19" s="30"/>
       <c r="I19" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
       <c r="N19" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O19" s="30"/>
       <c r="P19" s="30"/>
       <c r="Q19" s="30"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T19" s="30"/>
       <c r="U19" s="30"/>
       <c r="V19" s="30"/>
       <c r="W19" s="30"/>
       <c r="X19" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="30"/>
       <c r="Z19" s="30"/>
       <c r="AA19" s="30"/>
       <c r="AB19" s="30"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B20" s="31" t="s">
-        <v>402</v>
+      <c r="AC19" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B20" s="62" t="s">
+        <v>399</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D20" s="30"/>
       <c r="E20" s="30"/>
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
       <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="I20" s="30">
+        <v>9</v>
+      </c>
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
       <c r="L20" s="30"/>
       <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
+      <c r="N20" s="30">
+        <v>9</v>
+      </c>
       <c r="O20" s="30"/>
       <c r="P20" s="30"/>
       <c r="Q20" s="30"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30">
-        <v>-50</v>
+        <v>-7</v>
       </c>
       <c r="T20" s="30"/>
       <c r="U20" s="30"/>
       <c r="V20" s="30"/>
       <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
+      <c r="X20" s="30">
+        <v>9</v>
+      </c>
       <c r="Y20" s="30"/>
       <c r="Z20" s="30"/>
       <c r="AA20" s="30"/>
       <c r="AB20" s="30"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B21" s="31" t="s">
-        <v>404</v>
+      <c r="AC20" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B21" s="62" t="s">
+        <v>401</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="30"/>
@@ -6255,40 +6377,44 @@
       <c r="G21" s="30"/>
       <c r="H21" s="30"/>
       <c r="I21" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
       <c r="L21" s="30"/>
       <c r="M21" s="30"/>
       <c r="N21" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O21" s="30"/>
       <c r="P21" s="30"/>
       <c r="Q21" s="30"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T21" s="30"/>
       <c r="U21" s="30"/>
       <c r="V21" s="30"/>
       <c r="W21" s="30"/>
       <c r="X21" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y21" s="30"/>
       <c r="Z21" s="30"/>
       <c r="AA21" s="30"/>
       <c r="AB21" s="30"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B22" s="31" t="s">
-        <v>406</v>
+      <c r="AC21" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B22" s="62" t="s">
+        <v>403</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
@@ -6296,40 +6422,44 @@
       <c r="G22" s="30"/>
       <c r="H22" s="30"/>
       <c r="I22" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
       <c r="L22" s="30"/>
       <c r="M22" s="30"/>
       <c r="N22" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O22" s="30"/>
       <c r="P22" s="30"/>
       <c r="Q22" s="30"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T22" s="30"/>
       <c r="U22" s="30"/>
       <c r="V22" s="30"/>
       <c r="W22" s="30"/>
       <c r="X22" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="30"/>
       <c r="Z22" s="30"/>
       <c r="AA22" s="30"/>
       <c r="AB22" s="30"/>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B23" s="31" t="s">
-        <v>408</v>
+      <c r="AC22" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B23" s="62" t="s">
+        <v>405</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
@@ -6337,40 +6467,44 @@
       <c r="G23" s="30"/>
       <c r="H23" s="30"/>
       <c r="I23" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
       <c r="M23" s="30"/>
       <c r="N23" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O23" s="30"/>
       <c r="P23" s="30"/>
       <c r="Q23" s="30"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T23" s="30"/>
       <c r="U23" s="30"/>
       <c r="V23" s="30"/>
       <c r="W23" s="30"/>
       <c r="X23" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="30"/>
       <c r="Z23" s="30"/>
       <c r="AA23" s="30"/>
       <c r="AB23" s="30"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B24" s="31" t="s">
-        <v>409</v>
+      <c r="AC23" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B24" s="62" t="s">
+        <v>406</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D24" s="30"/>
       <c r="E24" s="30"/>
@@ -6378,40 +6512,44 @@
       <c r="G24" s="30"/>
       <c r="H24" s="30"/>
       <c r="I24" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
       <c r="L24" s="30"/>
       <c r="M24" s="30"/>
       <c r="N24" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O24" s="30"/>
       <c r="P24" s="30"/>
       <c r="Q24" s="30"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T24" s="30"/>
       <c r="U24" s="30"/>
       <c r="V24" s="30"/>
       <c r="W24" s="30"/>
       <c r="X24" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y24" s="30"/>
       <c r="Z24" s="30"/>
       <c r="AA24" s="30"/>
       <c r="AB24" s="30"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B25" s="31" t="s">
+      <c r="AC24" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B25" s="62" t="s">
+        <v>465</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>471</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>477</v>
       </c>
       <c r="D25" s="30"/>
       <c r="E25" s="30"/>
@@ -6419,40 +6557,44 @@
       <c r="G25" s="30"/>
       <c r="H25" s="30"/>
       <c r="I25" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
       <c r="L25" s="30"/>
       <c r="M25" s="30"/>
       <c r="N25" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O25" s="30"/>
       <c r="P25" s="30"/>
       <c r="Q25" s="30"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T25" s="30"/>
       <c r="U25" s="30"/>
       <c r="V25" s="30"/>
       <c r="W25" s="30"/>
       <c r="X25" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="30"/>
       <c r="Z25" s="30"/>
       <c r="AA25" s="30"/>
       <c r="AB25" s="30"/>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B26" s="31" t="s">
-        <v>411</v>
+      <c r="AC25" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B26" s="62" t="s">
+        <v>408</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D26" s="30"/>
       <c r="E26" s="30"/>
@@ -6460,40 +6602,44 @@
       <c r="G26" s="30"/>
       <c r="H26" s="30"/>
       <c r="I26" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
       <c r="L26" s="30"/>
       <c r="M26" s="30"/>
       <c r="N26" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O26" s="30"/>
       <c r="P26" s="30"/>
       <c r="Q26" s="30"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T26" s="30"/>
       <c r="U26" s="30"/>
       <c r="V26" s="30"/>
       <c r="W26" s="30"/>
       <c r="X26" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y26" s="30"/>
       <c r="Z26" s="30"/>
       <c r="AA26" s="30"/>
       <c r="AB26" s="30"/>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B27" s="31" t="s">
-        <v>413</v>
+      <c r="AC26" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B27" s="62" t="s">
+        <v>410</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
@@ -6501,40 +6647,44 @@
       <c r="G27" s="30"/>
       <c r="H27" s="30"/>
       <c r="I27" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J27" s="30"/>
       <c r="K27" s="30"/>
       <c r="L27" s="30"/>
       <c r="M27" s="30"/>
       <c r="N27" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O27" s="30"/>
       <c r="P27" s="30"/>
       <c r="Q27" s="30"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T27" s="30"/>
       <c r="U27" s="30"/>
       <c r="V27" s="30"/>
       <c r="W27" s="30"/>
       <c r="X27" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="30"/>
       <c r="Z27" s="30"/>
       <c r="AA27" s="30"/>
       <c r="AB27" s="30"/>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B28" s="31" t="s">
-        <v>415</v>
+      <c r="AC27" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B28" s="62" t="s">
+        <v>412</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
@@ -6542,40 +6692,44 @@
       <c r="G28" s="30"/>
       <c r="H28" s="30"/>
       <c r="I28" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
       <c r="M28" s="30"/>
       <c r="N28" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O28" s="30"/>
       <c r="P28" s="30"/>
       <c r="Q28" s="30"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T28" s="30"/>
       <c r="U28" s="30"/>
       <c r="V28" s="30"/>
       <c r="W28" s="30"/>
       <c r="X28" s="30">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Y28" s="30"/>
       <c r="Z28" s="30"/>
       <c r="AA28" s="30"/>
       <c r="AB28" s="30"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B29" s="31" t="s">
-        <v>417</v>
+      <c r="AC28" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B29" s="62" t="s">
+        <v>414</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
@@ -6583,40 +6737,44 @@
       <c r="G29" s="30"/>
       <c r="H29" s="30"/>
       <c r="I29" s="30">
-        <v>25</v>
+        <v>-7</v>
       </c>
       <c r="J29" s="30"/>
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
       <c r="M29" s="30"/>
       <c r="N29" s="30">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O29" s="30"/>
       <c r="P29" s="30"/>
       <c r="Q29" s="30"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T29" s="30"/>
       <c r="U29" s="30"/>
       <c r="V29" s="30"/>
       <c r="W29" s="30"/>
       <c r="X29" s="30">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Y29" s="30"/>
       <c r="Z29" s="30"/>
       <c r="AA29" s="30"/>
       <c r="AB29" s="30"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B30" s="31" t="s">
-        <v>419</v>
+      <c r="AC29" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B30" s="62" t="s">
+        <v>416</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D30" s="30"/>
       <c r="E30" s="30"/>
@@ -6624,40 +6782,44 @@
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="J30" s="30"/>
       <c r="K30" s="30"/>
       <c r="L30" s="30"/>
       <c r="M30" s="30"/>
       <c r="N30" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O30" s="30"/>
       <c r="P30" s="30"/>
       <c r="Q30" s="30"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T30" s="30"/>
       <c r="U30" s="30"/>
       <c r="V30" s="30"/>
       <c r="W30" s="30"/>
       <c r="X30" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="30"/>
       <c r="Z30" s="30"/>
       <c r="AA30" s="30"/>
       <c r="AB30" s="30"/>
-    </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B31" s="31" t="s">
-        <v>421</v>
+      <c r="AC30" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B31" s="62" t="s">
+        <v>418</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D31" s="30"/>
       <c r="E31" s="30"/>
@@ -6665,40 +6827,44 @@
       <c r="G31" s="30"/>
       <c r="H31" s="30"/>
       <c r="I31" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="J31" s="30"/>
       <c r="K31" s="30"/>
       <c r="L31" s="30"/>
       <c r="M31" s="30"/>
       <c r="N31" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="O31" s="30"/>
       <c r="P31" s="30"/>
       <c r="Q31" s="30"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="T31" s="30"/>
       <c r="U31" s="30"/>
       <c r="V31" s="30"/>
       <c r="W31" s="30"/>
       <c r="X31" s="30">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="Y31" s="30"/>
       <c r="Z31" s="30"/>
       <c r="AA31" s="30"/>
       <c r="AB31" s="30"/>
-    </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B32" s="31" t="s">
-        <v>423</v>
+      <c r="AC31" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B32" s="62" t="s">
+        <v>420</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D32" s="30"/>
       <c r="E32" s="30"/>
@@ -6706,40 +6872,44 @@
       <c r="G32" s="30"/>
       <c r="H32" s="30"/>
       <c r="I32" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
       <c r="L32" s="30"/>
       <c r="M32" s="30"/>
       <c r="N32" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O32" s="30"/>
       <c r="P32" s="30"/>
       <c r="Q32" s="30"/>
       <c r="R32" s="30"/>
       <c r="S32" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T32" s="30"/>
       <c r="U32" s="30"/>
       <c r="V32" s="30"/>
       <c r="W32" s="30"/>
       <c r="X32" s="30">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="30"/>
       <c r="Z32" s="30"/>
       <c r="AA32" s="30"/>
       <c r="AB32" s="30"/>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B33" s="31" t="s">
-        <v>425</v>
+      <c r="AC32" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B33" s="62" t="s">
+        <v>422</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D33" s="30"/>
       <c r="E33" s="30"/>
@@ -6747,40 +6917,44 @@
       <c r="G33" s="30"/>
       <c r="H33" s="30"/>
       <c r="I33" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="J33" s="30"/>
       <c r="K33" s="30"/>
       <c r="L33" s="30"/>
       <c r="M33" s="30"/>
       <c r="N33" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="O33" s="30"/>
       <c r="P33" s="30"/>
       <c r="Q33" s="30"/>
       <c r="R33" s="30"/>
       <c r="S33" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="T33" s="30"/>
       <c r="U33" s="30"/>
       <c r="V33" s="30"/>
       <c r="W33" s="30"/>
       <c r="X33" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="Y33" s="30"/>
       <c r="Z33" s="30"/>
       <c r="AA33" s="30"/>
       <c r="AB33" s="30"/>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B34" s="31" t="s">
-        <v>427</v>
+      <c r="AC33" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B34" s="62" t="s">
+        <v>424</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D34" s="30"/>
       <c r="E34" s="30"/>
@@ -6788,40 +6962,44 @@
       <c r="G34" s="30"/>
       <c r="H34" s="30"/>
       <c r="I34" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J34" s="30"/>
       <c r="K34" s="30"/>
       <c r="L34" s="30"/>
       <c r="M34" s="30"/>
       <c r="N34" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O34" s="30"/>
       <c r="P34" s="30"/>
       <c r="Q34" s="30"/>
       <c r="R34" s="30"/>
       <c r="S34" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T34" s="30"/>
       <c r="U34" s="30"/>
       <c r="V34" s="30"/>
       <c r="W34" s="30"/>
       <c r="X34" s="30">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="30"/>
       <c r="Z34" s="30"/>
       <c r="AA34" s="30"/>
       <c r="AB34" s="30"/>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B35" s="31" t="s">
-        <v>429</v>
+      <c r="AC34" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B35" s="62" t="s">
+        <v>426</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D35" s="30"/>
       <c r="E35" s="30"/>
@@ -6829,40 +7007,44 @@
       <c r="G35" s="30"/>
       <c r="H35" s="30"/>
       <c r="I35" s="30">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="J35" s="30"/>
       <c r="K35" s="30"/>
       <c r="L35" s="30"/>
       <c r="M35" s="30"/>
       <c r="N35" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="O35" s="30"/>
       <c r="P35" s="30"/>
       <c r="Q35" s="30"/>
       <c r="R35" s="30"/>
       <c r="S35" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="T35" s="30"/>
       <c r="U35" s="30"/>
       <c r="V35" s="30"/>
       <c r="W35" s="30"/>
       <c r="X35" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="Y35" s="30"/>
       <c r="Z35" s="30"/>
       <c r="AA35" s="30"/>
       <c r="AB35" s="30"/>
-    </row>
-    <row r="36" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B36" s="31" t="s">
-        <v>431</v>
+      <c r="AC35" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B36" s="62" t="s">
+        <v>428</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D36" s="30"/>
       <c r="E36" s="30"/>
@@ -6870,40 +7052,44 @@
       <c r="G36" s="30"/>
       <c r="H36" s="30"/>
       <c r="I36" s="30">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="J36" s="30"/>
       <c r="K36" s="30"/>
       <c r="L36" s="30"/>
       <c r="M36" s="30"/>
       <c r="N36" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O36" s="30"/>
       <c r="P36" s="30"/>
       <c r="Q36" s="30"/>
       <c r="R36" s="30"/>
       <c r="S36" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T36" s="30"/>
       <c r="U36" s="30"/>
       <c r="V36" s="30"/>
       <c r="W36" s="30"/>
       <c r="X36" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="30"/>
       <c r="Z36" s="30"/>
       <c r="AA36" s="30"/>
       <c r="AB36" s="30"/>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B37" s="31" t="s">
-        <v>433</v>
+      <c r="AC36" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B37" s="62" t="s">
+        <v>430</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D37" s="30"/>
       <c r="E37" s="30"/>
@@ -6911,40 +7097,44 @@
       <c r="G37" s="30"/>
       <c r="H37" s="30"/>
       <c r="I37" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="J37" s="30"/>
       <c r="K37" s="30"/>
       <c r="L37" s="30"/>
       <c r="M37" s="30"/>
       <c r="N37" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="O37" s="30"/>
       <c r="P37" s="30"/>
       <c r="Q37" s="30"/>
       <c r="R37" s="30"/>
       <c r="S37" s="30">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="T37" s="30"/>
       <c r="U37" s="30"/>
       <c r="V37" s="30"/>
       <c r="W37" s="30"/>
       <c r="X37" s="30">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="Y37" s="30"/>
       <c r="Z37" s="30"/>
       <c r="AA37" s="30"/>
       <c r="AB37" s="30"/>
-    </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B38" s="31" t="s">
-        <v>435</v>
+      <c r="AC37" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B38" s="62" t="s">
+        <v>432</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D38" s="30"/>
       <c r="E38" s="30"/>
@@ -6952,40 +7142,44 @@
       <c r="G38" s="30"/>
       <c r="H38" s="30"/>
       <c r="I38" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J38" s="30"/>
       <c r="K38" s="30"/>
       <c r="L38" s="30"/>
       <c r="M38" s="30"/>
       <c r="N38" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="O38" s="30"/>
       <c r="P38" s="30"/>
       <c r="Q38" s="30"/>
       <c r="R38" s="30"/>
       <c r="S38" s="30">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T38" s="30"/>
       <c r="U38" s="30"/>
       <c r="V38" s="30"/>
       <c r="W38" s="30"/>
       <c r="X38" s="30">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="Y38" s="30"/>
       <c r="Z38" s="30"/>
       <c r="AA38" s="30"/>
       <c r="AB38" s="30"/>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B39" s="31" t="s">
-        <v>437</v>
+      <c r="AC38" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B39" s="62" t="s">
+        <v>434</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D39" s="30"/>
       <c r="E39" s="30"/>
@@ -6993,40 +7187,44 @@
       <c r="G39" s="30"/>
       <c r="H39" s="30"/>
       <c r="I39" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
       <c r="L39" s="30"/>
       <c r="M39" s="30"/>
       <c r="N39" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="O39" s="30"/>
       <c r="P39" s="30"/>
       <c r="Q39" s="30"/>
       <c r="R39" s="30"/>
       <c r="S39" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="T39" s="30"/>
       <c r="U39" s="30"/>
       <c r="V39" s="30"/>
       <c r="W39" s="30"/>
       <c r="X39" s="30">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="Y39" s="30"/>
       <c r="Z39" s="30"/>
       <c r="AA39" s="30"/>
       <c r="AB39" s="30"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B40" s="31" t="s">
-        <v>439</v>
+      <c r="AC39" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B40" s="62" t="s">
+        <v>436</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D40" s="30"/>
       <c r="E40" s="30"/>
@@ -7034,474 +7232,1024 @@
       <c r="G40" s="30"/>
       <c r="H40" s="30"/>
       <c r="I40" s="30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
       <c r="M40" s="30"/>
       <c r="N40" s="30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O40" s="30"/>
       <c r="P40" s="30"/>
       <c r="Q40" s="30"/>
       <c r="R40" s="30"/>
       <c r="S40" s="30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T40" s="30"/>
       <c r="U40" s="30"/>
       <c r="V40" s="30"/>
       <c r="W40" s="30"/>
       <c r="X40" s="30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="30"/>
       <c r="Z40" s="30"/>
       <c r="AA40" s="30"/>
       <c r="AB40" s="30"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B41" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>442</v>
+      <c r="AC40" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B41" s="62" t="s">
+        <v>467</v>
+      </c>
+      <c r="C41" s="60" t="s">
+        <v>462</v>
       </c>
       <c r="D41" s="30"/>
       <c r="E41" s="30"/>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
       <c r="H41" s="30"/>
-      <c r="I41" s="30">
-        <v>-10</v>
+      <c r="I41" s="61">
+        <v>10</v>
       </c>
       <c r="J41" s="30"/>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
       <c r="M41" s="30"/>
-      <c r="N41" s="30">
-        <v>-10</v>
+      <c r="N41" s="61">
+        <v>10</v>
       </c>
       <c r="O41" s="30"/>
       <c r="P41" s="30"/>
       <c r="Q41" s="30"/>
       <c r="R41" s="30"/>
-      <c r="S41" s="30">
-        <v>-10</v>
+      <c r="S41" s="61">
+        <v>10</v>
       </c>
       <c r="T41" s="30"/>
       <c r="U41" s="30"/>
       <c r="V41" s="30"/>
       <c r="W41" s="30"/>
-      <c r="X41" s="30">
-        <v>-10</v>
+      <c r="X41" s="61">
+        <v>10</v>
       </c>
       <c r="Y41" s="30"/>
       <c r="Z41" s="30"/>
       <c r="AA41" s="30"/>
       <c r="AB41" s="30"/>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B42" s="31" t="s">
-        <v>473</v>
-      </c>
-      <c r="C42" s="38" t="s">
+      <c r="AC41" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B42" s="62" t="s">
         <v>468</v>
       </c>
-      <c r="I42" s="39">
+      <c r="C42" s="60" t="s">
+        <v>464</v>
+      </c>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="61">
+        <v>-17</v>
+      </c>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="61">
+        <v>19</v>
+      </c>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="61">
+        <v>19</v>
+      </c>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
+      <c r="X42" s="61">
+        <v>19</v>
+      </c>
+      <c r="Y42" s="30"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="30"/>
+      <c r="AB42" s="30"/>
+      <c r="AC42" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B43" s="62" t="s">
+        <v>469</v>
+      </c>
+      <c r="C43" s="60" t="s">
+        <v>463</v>
+      </c>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="61">
+        <v>19</v>
+      </c>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="61">
+        <v>19</v>
+      </c>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="61">
+        <v>19</v>
+      </c>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="61">
+        <v>-17</v>
+      </c>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="30"/>
+      <c r="AB43" s="30"/>
+      <c r="AC43" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B44" s="62" t="s">
+        <v>470</v>
+      </c>
+      <c r="C44" s="60" t="s">
+        <v>466</v>
+      </c>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30">
+        <v>0</v>
+      </c>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30">
+        <v>0</v>
+      </c>
+      <c r="O44" s="30"/>
+      <c r="P44" s="30"/>
+      <c r="Q44" s="30"/>
+      <c r="R44" s="30"/>
+      <c r="S44" s="30">
+        <v>0</v>
+      </c>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="30"/>
+      <c r="X44" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="30"/>
+      <c r="Z44" s="30"/>
+      <c r="AA44" s="30"/>
+      <c r="AB44" s="30"/>
+      <c r="AC44" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B45" s="62" t="s">
+        <v>479</v>
+      </c>
+      <c r="C45" s="60" t="s">
+        <v>489</v>
+      </c>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30">
+        <v>5</v>
+      </c>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30">
+        <v>5</v>
+      </c>
+      <c r="O45" s="30"/>
+      <c r="P45" s="30"/>
+      <c r="Q45" s="30"/>
+      <c r="R45" s="30"/>
+      <c r="S45" s="30">
+        <v>5</v>
+      </c>
+      <c r="T45" s="30"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="30"/>
+      <c r="W45" s="30"/>
+      <c r="X45" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="30"/>
+      <c r="Z45" s="30"/>
+      <c r="AA45" s="30"/>
+      <c r="AB45" s="30"/>
+      <c r="AC45" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="N42" s="39">
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B46" s="62" t="s">
+        <v>480</v>
+      </c>
+      <c r="C46" s="60" t="s">
+        <v>490</v>
+      </c>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30">
+        <v>0</v>
+      </c>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30">
+        <v>0</v>
+      </c>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30">
+        <v>0</v>
+      </c>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B47" s="62" t="s">
+        <v>481</v>
+      </c>
+      <c r="C47" s="60" t="s">
+        <v>491</v>
+      </c>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30">
+        <v>5</v>
+      </c>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30">
+        <v>5</v>
+      </c>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="S47" s="30">
+        <v>5</v>
+      </c>
+      <c r="T47" s="30"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="S42" s="39">
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="B48" s="62" t="s">
+        <v>482</v>
+      </c>
+      <c r="C48" s="60" t="s">
+        <v>492</v>
+      </c>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30">
+        <v>0</v>
+      </c>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30">
+        <v>0</v>
+      </c>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="S48" s="30">
+        <v>0</v>
+      </c>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B49" s="62" t="s">
+        <v>483</v>
+      </c>
+      <c r="C49" s="60" t="s">
+        <v>493</v>
+      </c>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30">
+        <v>5</v>
+      </c>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30">
+        <v>5</v>
+      </c>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30">
+        <v>5</v>
+      </c>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="X42" s="39">
+    </row>
+    <row r="50" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B50" s="62" t="s">
+        <v>484</v>
+      </c>
+      <c r="C50" s="60" t="s">
+        <v>494</v>
+      </c>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30">
+        <v>0</v>
+      </c>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30">
+        <v>0</v>
+      </c>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="S50" s="30">
+        <v>0</v>
+      </c>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="30"/>
+      <c r="X50" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="30"/>
+      <c r="Z50" s="30"/>
+      <c r="AA50" s="30"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B51" s="62" t="s">
+        <v>485</v>
+      </c>
+      <c r="C51" s="60" t="s">
+        <v>495</v>
+      </c>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30">
+        <v>5</v>
+      </c>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30">
+        <v>5</v>
+      </c>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30">
+        <v>5</v>
+      </c>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y51" s="30"/>
+      <c r="Z51" s="30"/>
+      <c r="AA51" s="30"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B43" s="31" t="s">
+    <row r="52" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B52" s="62" t="s">
+        <v>486</v>
+      </c>
+      <c r="C52" s="60" t="s">
+        <v>496</v>
+      </c>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30">
+        <v>0</v>
+      </c>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30">
+        <v>0</v>
+      </c>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30">
+        <v>0</v>
+      </c>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
+      <c r="AA52" s="30"/>
+      <c r="AB52" s="30"/>
+      <c r="AC52" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B53" s="62" t="s">
+        <v>487</v>
+      </c>
+      <c r="C53" s="60" t="s">
+        <v>497</v>
+      </c>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30">
+        <v>5</v>
+      </c>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30"/>
+      <c r="N53" s="30">
+        <v>5</v>
+      </c>
+      <c r="O53" s="30"/>
+      <c r="P53" s="30"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30">
+        <v>5</v>
+      </c>
+      <c r="T53" s="30"/>
+      <c r="U53" s="30"/>
+      <c r="V53" s="30"/>
+      <c r="W53" s="30"/>
+      <c r="X53" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y53" s="30"/>
+      <c r="Z53" s="30"/>
+      <c r="AA53" s="30"/>
+      <c r="AB53" s="30"/>
+      <c r="AC53" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B54" s="62" t="s">
+        <v>488</v>
+      </c>
+      <c r="C54" s="60" t="s">
+        <v>498</v>
+      </c>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30">
+        <v>0</v>
+      </c>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30"/>
+      <c r="N54" s="30">
+        <v>0</v>
+      </c>
+      <c r="O54" s="30"/>
+      <c r="P54" s="30"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30">
+        <v>0</v>
+      </c>
+      <c r="T54" s="30"/>
+      <c r="U54" s="30"/>
+      <c r="V54" s="30"/>
+      <c r="W54" s="30"/>
+      <c r="X54" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="30"/>
+      <c r="Z54" s="30"/>
+      <c r="AA54" s="30"/>
+      <c r="AB54" s="30"/>
+      <c r="AC54" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B55" s="62" t="s">
+        <v>499</v>
+      </c>
+      <c r="C55" s="60" t="s">
+        <v>500</v>
+      </c>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30">
+        <v>0</v>
+      </c>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30">
+        <v>0</v>
+      </c>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30">
+        <v>0</v>
+      </c>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
+      <c r="AA55" s="30"/>
+      <c r="AB55" s="30"/>
+      <c r="AC55" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B56" s="64">
+        <v>205001</v>
+      </c>
+      <c r="C56" s="60" t="s">
         <v>474</v>
       </c>
-      <c r="C43" s="38" t="s">
-        <v>470</v>
-      </c>
-      <c r="I43" s="39">
-        <v>-20</v>
-      </c>
-      <c r="N43" s="39">
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30">
+        <v>5</v>
+      </c>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30"/>
+      <c r="N56" s="30">
+        <v>5</v>
+      </c>
+      <c r="O56" s="30"/>
+      <c r="P56" s="30"/>
+      <c r="Q56" s="30"/>
+      <c r="R56" s="30"/>
+      <c r="S56" s="30">
+        <v>5</v>
+      </c>
+      <c r="T56" s="30"/>
+      <c r="U56" s="30"/>
+      <c r="V56" s="30"/>
+      <c r="W56" s="30"/>
+      <c r="X56" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y56" s="30"/>
+      <c r="Z56" s="30"/>
+      <c r="AA56" s="30"/>
+      <c r="AB56" s="30"/>
+      <c r="AC56" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="S43" s="39">
+    </row>
+    <row r="57" spans="2:30" s="59" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="65">
+        <v>205002</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>475</v>
+      </c>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41">
+        <v>10</v>
+      </c>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41">
+        <v>10</v>
+      </c>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
+      <c r="Q57" s="41"/>
+      <c r="R57" s="41"/>
+      <c r="S57" s="41">
+        <v>10</v>
+      </c>
+      <c r="T57" s="41"/>
+      <c r="U57" s="41"/>
+      <c r="V57" s="41"/>
+      <c r="W57" s="41"/>
+      <c r="X57" s="41">
+        <v>10</v>
+      </c>
+      <c r="Y57" s="41"/>
+      <c r="Z57" s="41"/>
+      <c r="AA57" s="41"/>
+      <c r="AB57" s="41"/>
+      <c r="AC57" s="40">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="AD57" s="40" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="58" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B58" s="64">
+        <v>205003</v>
+      </c>
+      <c r="C58" s="60" t="s">
+        <v>476</v>
+      </c>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30">
+        <v>0</v>
+      </c>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30">
+        <v>0</v>
+      </c>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30">
+        <v>0</v>
+      </c>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
+      <c r="AA58" s="30"/>
+      <c r="AB58" s="30"/>
+      <c r="AC58" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B59" s="66">
+        <v>206001</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30">
+        <v>5</v>
+      </c>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="30"/>
+      <c r="N59" s="30">
+        <v>5</v>
+      </c>
+      <c r="O59" s="30"/>
+      <c r="P59" s="30"/>
+      <c r="Q59" s="30"/>
+      <c r="R59" s="30"/>
+      <c r="S59" s="30">
+        <v>5</v>
+      </c>
+      <c r="T59" s="30"/>
+      <c r="U59" s="30"/>
+      <c r="V59" s="30"/>
+      <c r="W59" s="30"/>
+      <c r="X59" s="30">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="30"/>
+      <c r="Z59" s="30"/>
+      <c r="AA59" s="30"/>
+      <c r="AB59" s="30"/>
+      <c r="AC59" s="32">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="X43" s="39">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B44" s="31" t="s">
-        <v>475</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>469</v>
-      </c>
-      <c r="I44" s="39">
-        <v>20</v>
-      </c>
-      <c r="N44" s="39">
-        <v>20</v>
-      </c>
-      <c r="S44" s="39">
-        <v>20</v>
-      </c>
-      <c r="X44" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B45" s="31" t="s">
-        <v>476</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="I45" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N45" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S45" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X45" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B46" s="57" t="s">
-        <v>486</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>496</v>
-      </c>
-      <c r="I46" s="39">
-        <v>20</v>
-      </c>
-      <c r="N46" s="39">
-        <v>20</v>
-      </c>
-      <c r="S46" s="39">
-        <v>20</v>
-      </c>
-      <c r="X46" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B47" s="57" t="s">
-        <v>487</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="I47" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N47" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S47" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X47" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B48" s="57" t="s">
-        <v>488</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>498</v>
-      </c>
-      <c r="I48" s="39">
-        <v>20</v>
-      </c>
-      <c r="N48" s="39">
-        <v>20</v>
-      </c>
-      <c r="S48" s="39">
-        <v>20</v>
-      </c>
-      <c r="X48" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B49" s="57" t="s">
-        <v>489</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>499</v>
-      </c>
-      <c r="I49" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N49" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S49" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X49" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B50" s="57" t="s">
-        <v>490</v>
-      </c>
-      <c r="C50" s="38" t="s">
-        <v>500</v>
-      </c>
-      <c r="I50" s="39">
-        <v>20</v>
-      </c>
-      <c r="N50" s="39">
-        <v>20</v>
-      </c>
-      <c r="S50" s="39">
-        <v>20</v>
-      </c>
-      <c r="X50" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B51" s="57" t="s">
-        <v>491</v>
-      </c>
-      <c r="C51" s="38" t="s">
+    </row>
+    <row r="60" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B60" s="66">
+        <v>206002</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30">
+        <v>0</v>
+      </c>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="30"/>
+      <c r="N60" s="30">
+        <v>0</v>
+      </c>
+      <c r="O60" s="30"/>
+      <c r="P60" s="30"/>
+      <c r="Q60" s="30"/>
+      <c r="R60" s="30"/>
+      <c r="S60" s="30">
+        <v>0</v>
+      </c>
+      <c r="T60" s="30"/>
+      <c r="U60" s="30"/>
+      <c r="V60" s="30"/>
+      <c r="W60" s="30"/>
+      <c r="X60" s="30">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="30"/>
+      <c r="Z60" s="30"/>
+      <c r="AA60" s="30"/>
+      <c r="AB60" s="30"/>
+      <c r="AC60" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B61" s="66">
+        <v>207001</v>
+      </c>
+      <c r="C61" s="60" t="s">
         <v>501</v>
       </c>
-      <c r="I51" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N51" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S51" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X51" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B52" s="57" t="s">
-        <v>492</v>
-      </c>
-      <c r="C52" s="38" t="s">
-        <v>502</v>
-      </c>
-      <c r="I52" s="39">
-        <v>20</v>
-      </c>
-      <c r="N52" s="39">
-        <v>20</v>
-      </c>
-      <c r="S52" s="39">
-        <v>20</v>
-      </c>
-      <c r="X52" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B53" s="57" t="s">
-        <v>493</v>
-      </c>
-      <c r="C53" s="38" t="s">
-        <v>503</v>
-      </c>
-      <c r="I53" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N53" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S53" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X53" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B54" s="57" t="s">
-        <v>494</v>
-      </c>
-      <c r="C54" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="I54" s="39">
-        <v>20</v>
-      </c>
-      <c r="N54" s="39">
-        <v>20</v>
-      </c>
-      <c r="S54" s="39">
-        <v>20</v>
-      </c>
-      <c r="X54" s="39">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B55" s="57" t="s">
-        <v>495</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>505</v>
-      </c>
-      <c r="I55" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N55" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S55" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X55" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B56" s="57" t="s">
-        <v>506</v>
-      </c>
-      <c r="C56" s="38" t="s">
-        <v>507</v>
-      </c>
-      <c r="I56" s="39">
-        <v>-10</v>
-      </c>
-      <c r="N56" s="39">
-        <v>-10</v>
-      </c>
-      <c r="S56" s="39">
-        <v>-10</v>
-      </c>
-      <c r="X56" s="39">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B57" s="32">
-        <v>205001</v>
-      </c>
-      <c r="C57" s="38" t="s">
-        <v>481</v>
-      </c>
-      <c r="I57" s="39">
-        <v>20</v>
-      </c>
-      <c r="N57" s="39">
-        <v>20</v>
-      </c>
-      <c r="S57" s="39">
-        <v>20</v>
-      </c>
-      <c r="X57" s="39">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B58" s="32">
-        <v>205002</v>
-      </c>
-      <c r="C58" s="38" t="s">
-        <v>482</v>
-      </c>
-      <c r="I58" s="41">
-        <v>50</v>
-      </c>
-      <c r="N58" s="41">
-        <v>50</v>
-      </c>
-      <c r="S58" s="41">
-        <v>50</v>
-      </c>
-      <c r="X58" s="41">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B59" s="32">
-        <v>205003</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>483</v>
-      </c>
-      <c r="I59" s="41">
-        <v>-10</v>
-      </c>
-      <c r="N59" s="41">
-        <v>-10</v>
-      </c>
-      <c r="S59" s="41">
-        <v>-10</v>
-      </c>
-      <c r="X59" s="41">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B60" s="41">
-        <v>206001</v>
-      </c>
-      <c r="C60" s="32" t="s">
-        <v>485</v>
-      </c>
-      <c r="I60" s="41">
-        <v>25</v>
-      </c>
-      <c r="N60" s="41">
-        <v>25</v>
-      </c>
-      <c r="S60" s="41">
-        <v>25</v>
-      </c>
-      <c r="X60" s="41">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.3">
-      <c r="B61" s="41">
-        <v>206002</v>
-      </c>
-      <c r="C61" s="32" t="s">
-        <v>484</v>
-      </c>
-      <c r="I61" s="41">
-        <v>-10</v>
-      </c>
-      <c r="N61" s="41">
-        <v>-10</v>
-      </c>
-      <c r="S61" s="41">
-        <v>-10</v>
-      </c>
-      <c r="X61" s="41">
-        <v>-10</v>
-      </c>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="61">
+        <v>10</v>
+      </c>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="61">
+        <v>10</v>
+      </c>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="61">
+        <v>10</v>
+      </c>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="61">
+        <v>10</v>
+      </c>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30"/>
+      <c r="AC61" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42">
+        <f>SUM(I5:I61)</f>
+        <v>132</v>
+      </c>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
+      <c r="L62" s="42"/>
+      <c r="M62" s="42"/>
+      <c r="N62" s="42">
+        <f>SUM(N5:N61)</f>
+        <v>216</v>
+      </c>
+      <c r="O62" s="42"/>
+      <c r="P62" s="42"/>
+      <c r="Q62" s="42"/>
+      <c r="R62" s="42"/>
+      <c r="S62" s="42">
+        <f>SUM(S5:S61)</f>
+        <v>200</v>
+      </c>
+      <c r="T62" s="42"/>
+      <c r="U62" s="42"/>
+      <c r="V62" s="42"/>
+      <c r="W62" s="42"/>
+      <c r="X62" s="42">
+        <f>SUM(X5:X61)</f>
+        <v>132</v>
+      </c>
+      <c r="Y62" s="42"/>
+      <c r="Z62" s="42"/>
+      <c r="AA62" s="42"/>
+      <c r="AB62" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7555,57 +8303,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="53" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="51" t="s">
-        <v>443</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>444</v>
-      </c>
-      <c r="E2" s="56" t="s">
+      <c r="C2" s="53" t="s">
+        <v>438</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>439</v>
+      </c>
+      <c r="E2" s="58" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="47" t="s">
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="49" t="s">
         <v>336</v>
       </c>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="48" t="s">
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="50" t="s">
         <v>337</v>
       </c>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="50" t="s">
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="52" t="s">
         <v>338</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="49" t="s">
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="51" t="s">
         <v>339</v>
       </c>
-      <c r="Y2" s="45"/>
-      <c r="Z2" s="45"/>
-      <c r="AA2" s="45"/>
-      <c r="AB2" s="46"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47"/>
+      <c r="AA2" s="47"/>
+      <c r="AB2" s="48"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>340</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="25" t="s">
         <v>40</v>
       </c>
@@ -7761,14 +8509,14 @@
     </row>
     <row r="5" spans="1:28" ht="33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C5" s="31"/>
-      <c r="D5" s="40" t="s">
-        <v>480</v>
+      <c r="D5" s="38" t="s">
+        <v>473</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -7805,7 +8553,7 @@
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -7844,7 +8592,7 @@
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B7" s="31" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
@@ -7925,21 +8673,21 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -7947,7 +8695,7 @@
     </row>
     <row r="4" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7955,7 +8703,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -7963,7 +8711,7 @@
     </row>
     <row r="6" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -7971,7 +8719,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7979,7 +8727,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -7987,7 +8735,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -7995,7 +8743,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -8003,7 +8751,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -8011,7 +8759,7 @@
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -8019,7 +8767,7 @@
     </row>
     <row r="13" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -8027,7 +8775,7 @@
     </row>
     <row r="14" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -8059,13 +8807,13 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="220.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="5" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -8165,13 +8913,13 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="46"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="48"/>
     </row>
     <row r="15" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
